--- a/artfynd/A 13026-2022 artfynd.xlsx
+++ b/artfynd/A 13026-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13026-2022 artfynd.xlsx
+++ b/artfynd/A 13026-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99550530</v>
+        <v>133460864</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
+          <t>Gråmalen, Gråmalen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624411.0701598374</v>
+        <v>624635</v>
       </c>
       <c r="R2" t="n">
-        <v>6873170.576075901</v>
+        <v>6873160</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,86 +761,63 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99549855</v>
+        <v>133463129</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
+          <t>Timmerslätten, Timmerslätten, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624250.7847351664</v>
+        <v>624673</v>
       </c>
       <c r="R3" t="n">
-        <v>6872964.674836676</v>
+        <v>6873173</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,90 +855,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99550569</v>
+        <v>133462712</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
+          <t>Timmerslätten, Timmerslätten, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624384.9042468143</v>
+        <v>624601</v>
       </c>
       <c r="R4" t="n">
-        <v>6873177.149623272</v>
+        <v>6873237</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,53 +952,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99550646</v>
+        <v>99549631</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1111,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624097.9043142105</v>
+        <v>624305</v>
       </c>
       <c r="R5" t="n">
-        <v>6872955.797839055</v>
+        <v>6872943</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1144,19 +1041,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,9 +1066,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Späd torraka.</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Späd torraka.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,19 +1091,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99550027</v>
+        <v>99549855</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1242,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624359.0979233512</v>
+        <v>624251</v>
       </c>
       <c r="R6" t="n">
-        <v>6873070.77398622</v>
+        <v>6872964</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1275,19 +1162,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,19 +1207,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99549631</v>
+        <v>99550027</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1373,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624304.8408698929</v>
+        <v>624359</v>
       </c>
       <c r="R7" t="n">
-        <v>6872943.11522136</v>
+        <v>6873071</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1406,19 +1278,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,14 +1303,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Späd torraka.</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Späd torraka.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1466,19 +1323,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99550564</v>
+        <v>99550530</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1509,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624397.9474416794</v>
+        <v>624411</v>
       </c>
       <c r="R8" t="n">
-        <v>6873181.392103192</v>
+        <v>6873170</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1542,19 +1394,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,16 +1442,11 @@
         <v>99550553</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1640,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624402.2980126623</v>
+        <v>624402</v>
       </c>
       <c r="R9" t="n">
-        <v>6873165.548434019</v>
+        <v>6873165</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1673,19 +1510,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1728,65 +1555,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99547931</v>
+        <v>99550564</v>
       </c>
       <c r="B10" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Vålmyrknallen, Mellanfjärden, Nordanstig, Hls</t>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624495.6097330088</v>
+        <v>624398</v>
       </c>
       <c r="R10" t="n">
-        <v>6873024.463661861</v>
+        <v>6873181</v>
       </c>
       <c r="S10" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,29 +1626,35 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1852,19 +1671,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99550768</v>
+        <v>99550569</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1895,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624125.6078171858</v>
+        <v>624385</v>
       </c>
       <c r="R11" t="n">
-        <v>6872894.205470844</v>
+        <v>6873177</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1928,19 +1742,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1983,48 +1787,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133460511</v>
+        <v>99550646</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gråmalen, Gråmalen, Hls</t>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624613</v>
+        <v>624098</v>
       </c>
       <c r="R12" t="n">
-        <v>6873091</v>
+        <v>6872956</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2048,12 +1855,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2062,66 +1869,85 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133460946</v>
+        <v>99550768</v>
       </c>
       <c r="B13" t="n">
-        <v>58658</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gråmalen, Gråmalen, Hls</t>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624632</v>
+        <v>624125</v>
       </c>
       <c r="R13" t="n">
-        <v>6873167</v>
+        <v>6872894</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2145,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,66 +1985,85 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133461649</v>
+        <v>99551060</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norra Vålmyrknallen, Norra Vålmyrknallen, Hls</t>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624546</v>
+        <v>624115</v>
       </c>
       <c r="R14" t="n">
-        <v>6873182</v>
+        <v>6872860</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2242,12 +2087,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,28 +2101,44 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133463129</v>
+        <v>99551376</v>
       </c>
       <c r="B15" t="n">
-        <v>79426</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,34 +2146,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Timmerslätten, Timmerslätten, Hls</t>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624673</v>
+        <v>624118</v>
       </c>
       <c r="R15" t="n">
-        <v>6873173</v>
+        <v>6872836</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,12 +2203,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,66 +2217,88 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>3 substratenheter # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133461323</v>
+        <v>99551510</v>
       </c>
       <c r="B16" t="n">
-        <v>5497</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101410</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norra Vålmyrknallen, Norra Vålmyrknallen, Hls</t>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624557</v>
+        <v>624252</v>
       </c>
       <c r="R16" t="n">
-        <v>6873159</v>
+        <v>6872890</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2436,12 +2322,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2450,28 +2336,47 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133463226</v>
+        <v>133461649</v>
       </c>
       <c r="B17" t="n">
-        <v>80474</v>
+        <v>79130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,34 +2384,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Timmerslätten, Timmerslätten, Hls</t>
+          <t>Norra Vålmyrknallen, Norra Vålmyrknallen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624689</v>
+        <v>624546</v>
       </c>
       <c r="R17" t="n">
-        <v>6873167</v>
+        <v>6873182</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2565,64 +2470,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133461826</v>
+        <v>133463226</v>
       </c>
       <c r="B18" t="n">
-        <v>57165</v>
+        <v>80488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norra Vålmyrknallen, Norra Vålmyrknallen, Hls</t>
+          <t>Timmerslätten, Timmerslätten, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624546</v>
+        <v>624689</v>
       </c>
       <c r="R18" t="n">
-        <v>6873195</v>
+        <v>6873167</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133462712</v>
+        <v>133460511</v>
       </c>
       <c r="B19" t="n">
-        <v>91922</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,34 +2578,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Timmerslätten, Timmerslätten, Hls</t>
+          <t>Gråmalen, Gråmalen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624601</v>
+        <v>624613</v>
       </c>
       <c r="R19" t="n">
-        <v>6873237</v>
+        <v>6873091</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2785,7 +2671,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2875,51 +2761,60 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133460864</v>
+        <v>105402684</v>
       </c>
       <c r="B21" t="n">
-        <v>92228</v>
+        <v>57945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>100110</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gråmalen, Gråmalen, Hls</t>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624635</v>
+        <v>624198</v>
       </c>
       <c r="R21" t="n">
-        <v>6873160</v>
+        <v>6872978</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2943,12 +2838,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,22 +2852,678 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Mats Axbrink</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>99551162</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>N Vålmyrknallen, Mellanfjärden, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>624115</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6872860</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133461323</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5497</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norra Vålmyrknallen, Norra Vålmyrknallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>624557</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6873159</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Magnus Lilja</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Magnus Lilja</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>99547925</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>N Vålmyrknallen, Mellanfjärden, Nordanstig, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>624100</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6872953</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133461826</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norra Vålmyrknallen, Norra Vålmyrknallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>624546</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6873195</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>99547931</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>N Vålmyrknallen, Mellanfjärden, Nordanstig, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>624496</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6873024</v>
+      </c>
+      <c r="S26" t="n">
+        <v>55</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133460946</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gråmalen, Gråmalen, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>624632</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6873167</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13026-2022 artfynd.xlsx
+++ b/artfynd/A 13026-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133460864</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133463129</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133462712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99549631</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99549855</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99550027</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99550530</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99550553</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99550564</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99550569</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1900,6 +1955,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99550646</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99550768</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2132,6 +2197,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99551060</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2251,6 +2321,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99551376</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2370,6 +2445,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99551510</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2467,6 +2547,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133461649</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2564,6 +2649,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133463226</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2661,6 +2751,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133460511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2758,6 +2853,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133461245</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2867,6 +2967,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105402684</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2972,6 +3077,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99551162</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3069,6 +3179,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133461323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3192,6 +3307,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99547925</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3308,6 +3428,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133461826</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3427,6 +3552,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99547931</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3524,8 +3654,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133460946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>